--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.55924954068825</v>
+        <v>7.24087805036184</v>
       </c>
       <c r="D2" t="n">
-        <v>44.33678085177291</v>
+        <v>7.204726888413098</v>
       </c>
       <c r="E2" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F2" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>88.70530662063614</v>
+        <v>14.41461232585337</v>
       </c>
       <c r="D3" t="n">
-        <v>39.66045119371297</v>
+        <v>6.444823318978358</v>
       </c>
       <c r="E3" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F3" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.9414148148061</v>
+        <v>6.327979907405992</v>
       </c>
       <c r="D4" t="n">
-        <v>38.79840041397111</v>
+        <v>6.304740067270306</v>
       </c>
       <c r="E4" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F4" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>76.39655435793327</v>
+        <v>12.41444008316416</v>
       </c>
       <c r="D5" t="n">
-        <v>35.85464482539962</v>
+        <v>5.82637978412744</v>
       </c>
       <c r="E5" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F5" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>58.17409511748838</v>
+        <v>9.453290456591862</v>
       </c>
       <c r="D6" t="n">
-        <v>53.37732560637418</v>
+        <v>8.673815411035804</v>
       </c>
       <c r="E6" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F6" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>46.57377124391024</v>
+        <v>7.568237827135415</v>
       </c>
       <c r="D7" t="n">
-        <v>46.13840930034276</v>
+        <v>7.497491511305698</v>
       </c>
       <c r="E7" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F7" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.14401384224284</v>
+        <v>4.898402249364461</v>
       </c>
       <c r="D8" t="n">
-        <v>30.51114661073239</v>
+        <v>4.958061324244014</v>
       </c>
       <c r="E8" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F8" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>77.42802434606639</v>
+        <v>12.58205395623579</v>
       </c>
       <c r="D9" t="n">
-        <v>27.81363150512662</v>
+        <v>4.519715119583076</v>
       </c>
       <c r="E9" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F9" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.19111387524811</v>
+        <v>3.931056004727818</v>
       </c>
       <c r="D10" t="n">
-        <v>24.27952412770885</v>
+        <v>3.945422670752688</v>
       </c>
       <c r="E10" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F10" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>40.81305166798659</v>
+        <v>6.632120896047821</v>
       </c>
       <c r="D11" t="n">
-        <v>40.2743727770891</v>
+        <v>6.544585576276979</v>
       </c>
       <c r="E11" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F11" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>57.78716739948375</v>
+        <v>9.390414702416109</v>
       </c>
       <c r="D12" t="n">
-        <v>29.90772846978222</v>
+        <v>4.860005876339612</v>
       </c>
       <c r="E12" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F12" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.07206310614267</v>
+        <v>4.074210254748184</v>
       </c>
       <c r="D13" t="n">
-        <v>24.60594300339991</v>
+        <v>3.998465738052486</v>
       </c>
       <c r="E13" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F13" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>18.38030715230949</v>
+        <v>2.986799912250293</v>
       </c>
       <c r="D14" t="n">
-        <v>18.88085330430665</v>
+        <v>3.068138661949831</v>
       </c>
       <c r="E14" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F14" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>56.04171540036567</v>
+        <v>9.106778752559423</v>
       </c>
       <c r="D15" t="n">
-        <v>14.94062322067665</v>
+        <v>2.427851273359956</v>
       </c>
       <c r="E15" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F15" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>36.51770140369982</v>
+        <v>5.934126478101221</v>
       </c>
       <c r="D16" t="n">
-        <v>35.85721869482441</v>
+        <v>5.826798037908967</v>
       </c>
       <c r="E16" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F16" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>16.71992585616087</v>
+        <v>2.716987951626141</v>
       </c>
       <c r="D17" t="n">
-        <v>16.21184281755741</v>
+        <v>2.63442445785308</v>
       </c>
       <c r="E17" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F17" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>11.56481828698551</v>
+        <v>1.879282971635146</v>
       </c>
       <c r="D18" t="n">
-        <v>11.32964655078002</v>
+        <v>1.841067564501754</v>
       </c>
       <c r="E18" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F18" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>43.65505020385815</v>
+        <v>7.093945658126949</v>
       </c>
       <c r="D19" t="n">
-        <v>42.64675271646966</v>
+        <v>6.93009731642632</v>
       </c>
       <c r="E19" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F19" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>41.01192020110547</v>
+        <v>6.664437032679639</v>
       </c>
       <c r="D20" t="n">
-        <v>28.50909155328798</v>
+        <v>4.632727377409297</v>
       </c>
       <c r="E20" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F20" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>11.52035441531474</v>
+        <v>1.872057592488645</v>
       </c>
       <c r="D21" t="n">
-        <v>10.83309321523127</v>
+        <v>1.760377647475082</v>
       </c>
       <c r="E21" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F21" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>60.57787002330388</v>
+        <v>9.843903878786881</v>
       </c>
       <c r="D22" t="n">
-        <v>13.0730028193223</v>
+        <v>2.124362958139873</v>
       </c>
       <c r="E22" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F22" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>37.54916255305473</v>
+        <v>6.101738914871394</v>
       </c>
       <c r="D23" t="n">
-        <v>36.6134912552286</v>
+        <v>5.949692328974647</v>
       </c>
       <c r="E23" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F23" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>11.0098077748061</v>
+        <v>1.78909376340599</v>
       </c>
       <c r="D24" t="n">
-        <v>11.55444580884544</v>
+        <v>1.877597443937384</v>
       </c>
       <c r="E24" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F24" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>31.16404042885121</v>
+        <v>5.064156569688322</v>
       </c>
       <c r="D25" t="n">
-        <v>26.11070544562257</v>
+        <v>4.242989634913669</v>
       </c>
       <c r="E25" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F25" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>21.57562142440166</v>
+        <v>3.506038481465269</v>
       </c>
       <c r="D26" t="n">
-        <v>20.88090073440604</v>
+        <v>3.393146369340982</v>
       </c>
       <c r="E26" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F26" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>26.09091726403925</v>
+        <v>4.239774055406379</v>
       </c>
       <c r="D27" t="n">
-        <v>25.06410281627577</v>
+        <v>4.072916707644812</v>
       </c>
       <c r="E27" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F27" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>17.92905907534836</v>
+        <v>2.913472099744108</v>
       </c>
       <c r="D28" t="n">
-        <v>17.38145946214118</v>
+        <v>2.824487162597941</v>
       </c>
       <c r="E28" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F28" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>48.05890542138381</v>
+        <v>7.809572130974868</v>
       </c>
       <c r="D29" t="n">
-        <v>8.55887917983533</v>
+        <v>1.390817866723241</v>
       </c>
       <c r="E29" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F29" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>26.7976051010647</v>
+        <v>4.354610828923014</v>
       </c>
       <c r="D30" t="n">
-        <v>25.91807620845192</v>
+        <v>4.211687383873437</v>
       </c>
       <c r="E30" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F30" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>27.87392487130782</v>
+        <v>4.529512791587521</v>
       </c>
       <c r="D31" t="n">
-        <v>27.31773378440218</v>
+        <v>4.439131739965354</v>
       </c>
       <c r="E31" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F31" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>17.96774782994029</v>
+        <v>2.919759022365297</v>
       </c>
       <c r="D32" t="n">
-        <v>17.10011374520163</v>
+        <v>2.778768483595264</v>
       </c>
       <c r="E32" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F32" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>21.96522588815758</v>
+        <v>3.569349206825607</v>
       </c>
       <c r="D33" t="n">
-        <v>21.73445837647796</v>
+        <v>3.531849486177669</v>
       </c>
       <c r="E33" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F33" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>27.83450624731177</v>
+        <v>4.523107265188163</v>
       </c>
       <c r="D34" t="n">
-        <v>27.54134356329924</v>
+        <v>4.475468329036127</v>
       </c>
       <c r="E34" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F34" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>13.35220342949056</v>
+        <v>2.169733057292215</v>
       </c>
       <c r="D35" t="n">
-        <v>12.32109109004107</v>
+        <v>2.002177302131674</v>
       </c>
       <c r="E35" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F35" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>19.43885251157591</v>
+        <v>3.158813533131086</v>
       </c>
       <c r="D36" t="n">
-        <v>18.86081973723542</v>
+        <v>3.064883207300755</v>
       </c>
       <c r="E36" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F36" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>35.58520631861405</v>
+        <v>5.782596026774783</v>
       </c>
       <c r="D37" t="n">
-        <v>35.04071199221628</v>
+        <v>5.694115698735146</v>
       </c>
       <c r="E37" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F37" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>38.56279785379606</v>
+        <v>6.266454651241859</v>
       </c>
       <c r="D38" t="n">
-        <v>11.92678959461715</v>
+        <v>1.938103309125287</v>
       </c>
       <c r="E38" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F38" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>47.60976110619239</v>
+        <v>7.736586179756263</v>
       </c>
       <c r="D39" t="n">
-        <v>22.09583955079542</v>
+        <v>3.590573927004256</v>
       </c>
       <c r="E39" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F39" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>22.20806408754771</v>
+        <v>3.608810414226503</v>
       </c>
       <c r="D40" t="n">
-        <v>22.31569784524587</v>
+        <v>3.626300899852454</v>
       </c>
       <c r="E40" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F40" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>52.67017307932339</v>
+        <v>8.558903125390051</v>
       </c>
       <c r="D41" t="n">
-        <v>34.53678859347481</v>
+        <v>5.612228146439657</v>
       </c>
       <c r="E41" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F41" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>4.329705158246764</v>
+        <v>0.7035770882150991</v>
       </c>
       <c r="D42" t="n">
-        <v>5.372268499986276</v>
+        <v>0.8729936312477699</v>
       </c>
       <c r="E42" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F42" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>41.20322320545753</v>
+        <v>6.695523770886848</v>
       </c>
       <c r="D43" t="n">
-        <v>31.3716488646779</v>
+        <v>5.097892940510159</v>
       </c>
       <c r="E43" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F43" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>17.09412431747685</v>
+        <v>2.777795201589988</v>
       </c>
       <c r="D44" t="n">
-        <v>17.73018033086949</v>
+        <v>2.881154303766293</v>
       </c>
       <c r="E44" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F44" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>14.64624584496854</v>
+        <v>2.380014949807387</v>
       </c>
       <c r="D45" t="n">
-        <v>15.54972516060979</v>
+        <v>2.52683033859909</v>
       </c>
       <c r="E45" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F45" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>32.97042581422795</v>
+        <v>5.357694194812042</v>
       </c>
       <c r="D46" t="n">
-        <v>20.992637488938</v>
+        <v>3.411303591952425</v>
       </c>
       <c r="E46" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F46" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>28.92086270798661</v>
+        <v>4.699640190047824</v>
       </c>
       <c r="D47" t="n">
-        <v>29.53221134106694</v>
+        <v>4.798984342923378</v>
       </c>
       <c r="E47" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F47" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>57.79707092645368</v>
+        <v>9.392024025548723</v>
       </c>
       <c r="D48" t="n">
-        <v>57.78976049020918</v>
+        <v>9.390836079658991</v>
       </c>
       <c r="E48" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F48" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>29.03081374159036</v>
+        <v>4.717507233008433</v>
       </c>
       <c r="D49" t="n">
-        <v>13.58639433671743</v>
+        <v>2.207789079716583</v>
       </c>
       <c r="E49" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F49" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>48.85004528279291</v>
+        <v>7.938132358453848</v>
       </c>
       <c r="D50" t="n">
-        <v>34.61008374958593</v>
+        <v>5.624138609307713</v>
       </c>
       <c r="E50" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F50" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>58.6159044777085</v>
+        <v>9.525084477627631</v>
       </c>
       <c r="D51" t="n">
-        <v>44.84014050138173</v>
+        <v>7.286522831474532</v>
       </c>
       <c r="E51" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F51" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>27.30542395323359</v>
+        <v>4.437131392400459</v>
       </c>
       <c r="D52" t="n">
-        <v>14.25664183976335</v>
+        <v>2.316704298961545</v>
       </c>
       <c r="E52" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F52" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>64.89586048056131</v>
+        <v>10.54557732809121</v>
       </c>
       <c r="D53" t="n">
-        <v>51.16434027069214</v>
+        <v>8.314205293987474</v>
       </c>
       <c r="E53" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F53" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>45.76121411375673</v>
+        <v>7.436197293485469</v>
       </c>
       <c r="D54" t="n">
-        <v>46.14788697056555</v>
+        <v>7.499031632716902</v>
       </c>
       <c r="E54" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F54" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>64.28793276622638</v>
+        <v>10.44678907451179</v>
       </c>
       <c r="D55" t="n">
-        <v>63.53967080769596</v>
+        <v>10.32519650625059</v>
       </c>
       <c r="E55" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F55" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>36.13193223829461</v>
+        <v>5.871438988722875</v>
       </c>
       <c r="D56" t="n">
-        <v>33.46959751415324</v>
+        <v>5.438809596049901</v>
       </c>
       <c r="E56" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F56" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>41.8419032242676</v>
+        <v>6.799309273943486</v>
       </c>
       <c r="D57" t="n">
-        <v>26.99849075807678</v>
+        <v>4.387254748187478</v>
       </c>
       <c r="E57" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F57" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>44.43845585930239</v>
+        <v>7.22124907713664</v>
       </c>
       <c r="D58" t="n">
-        <v>35.29960966650902</v>
+        <v>5.736186570807716</v>
       </c>
       <c r="E58" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F58" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>83.83153593685211</v>
+        <v>13.62262458973847</v>
       </c>
       <c r="D59" t="n">
-        <v>70.23176379223912</v>
+        <v>11.41266161623886</v>
       </c>
       <c r="E59" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F59" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>54.85781455625689</v>
+        <v>8.914394865391746</v>
       </c>
       <c r="D60" t="n">
-        <v>49.85207226660255</v>
+        <v>8.100961743322916</v>
       </c>
       <c r="E60" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F60" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2368,16 +2368,16 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>82.51484496821928</v>
+        <v>13.40866230733563</v>
       </c>
       <c r="D61" t="n">
-        <v>67.12343008853408</v>
+        <v>10.90755738938679</v>
       </c>
       <c r="E61" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F61" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2400,16 +2400,16 @@
         <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>89.3880124039532</v>
+        <v>14.5255520156424</v>
       </c>
       <c r="D62" t="n">
-        <v>74.09147920707714</v>
+        <v>12.03986537115004</v>
       </c>
       <c r="E62" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F62" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2432,16 +2432,16 @@
         <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>73.98797437544719</v>
+        <v>12.02304583601017</v>
       </c>
       <c r="D63" t="n">
-        <v>58.84713158492598</v>
+        <v>9.562658882550473</v>
       </c>
       <c r="E63" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F63" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         <v>63</v>
       </c>
       <c r="C64" t="n">
-        <v>87.7704472819799</v>
+        <v>14.26269768332173</v>
       </c>
       <c r="D64" t="n">
-        <v>86.69225120024251</v>
+        <v>14.08749082003941</v>
       </c>
       <c r="E64" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F64" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2496,16 +2496,16 @@
         <v>64</v>
       </c>
       <c r="C65" t="n">
-        <v>72.68893915632528</v>
+        <v>11.81195261290286</v>
       </c>
       <c r="D65" t="n">
-        <v>58.65204551085919</v>
+        <v>9.530957395514619</v>
       </c>
       <c r="E65" t="n">
-        <v>21.78433246964366</v>
+        <v>3.539954026317095</v>
       </c>
       <c r="F65" t="n">
-        <v>17.59604919117339</v>
+        <v>2.859357993565676</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
